--- a/XBRL-template-MPERS/Company/12-Notes-AccountingPolicies.xlsx
+++ b/XBRL-template-MPERS/Company/12-Notes-AccountingPolicies.xlsx
@@ -442,364 +442,364 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Disclosure on summary significant accounting policies [abstract]</t>
+          <t>Disclosure on summary significant accounting policies</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Disclosure of significant accounting policies [text block]</t>
+          <t>Disclosure of significant accounting policies</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Description of accounting policy for amortisation [text block]</t>
+          <t>Description of accounting policy for amortisation</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Description of accounting policy for biological assets [text block]</t>
+          <t>Description of accounting policy for biological assets</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Description of accounting policy for borrowing costs [text block]</t>
+          <t>Description of accounting policy for borrowing costs</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Description of accounting policy for borrowings [text block]</t>
+          <t>Description of accounting policy for borrowings</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Description of accounting policy for business combinations [text block]</t>
+          <t>Description of accounting policy for business combinations</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Description of accounting policy for cash and cash equivalents [text block]</t>
+          <t>Description of accounting policy for cash and cash equivalents</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Description of accounting policy for collateral [text block]</t>
+          <t>Description of accounting policy for collateral</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Description of accounting policy for construction contracts [text block]</t>
+          <t>Description of accounting policy for construction contracts</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Description of accounting policy for contingent assets [text block]</t>
+          <t>Description of accounting policy for contingent assets</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Description of accounting policy for contingent liabilities [text block]</t>
+          <t>Description of accounting policy for contingent liabilities</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Description of accounting policy for decommissioning, restoration and rehabilitation provisions [text block]</t>
+          <t>Description of accounting policy for decommissioning, restoration and rehabilitation provisions</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Description of accounting policy for deferred income tax [text block]</t>
+          <t>Description of accounting policy for deferred income tax</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Description of accounting policy for depreciation expense [text block]</t>
+          <t>Description of accounting policy for depreciation expense</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Description of accounting policy for dividend income [text block]</t>
+          <t>Description of accounting policy for dividend income</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Description of accounting policy for earnings per share [text block]</t>
+          <t>Description of accounting policy for earnings per share</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Description of accounting policy for employee benefits [text block]</t>
+          <t>Description of accounting policy for employee benefits</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Description of accounting policy for equity instruments [text block]</t>
+          <t>Description of accounting policy for equity instruments</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Description of accounting policy for fee and commission income and expense [text block]</t>
+          <t>Description of accounting policy for fee and commission income and expense</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Description of accounting policy for financial instruments [text block]</t>
+          <t>Description of accounting policy for financial instruments</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Description of accounting policy for foreign currency [text block]</t>
+          <t>Description of accounting policy for foreign currency</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Description of accounting policy for functional and presentation currency [text block]</t>
+          <t>Description of accounting policy for functional and presentation currency</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Description of accounting policy for goods sold [text block]</t>
+          <t>Description of accounting policy for goods sold</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Description of accounting policy for goodwill [text block]</t>
+          <t>Description of accounting policy for goodwill</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Description of accounting policy for government grants [text block]</t>
+          <t>Description of accounting policy for government grants</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Description of accounting policy for impairment of non-financial assets [text block]</t>
+          <t>Description of accounting policy for impairment of non-financial assets</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Description of accounting policy for income tax [text block]</t>
+          <t>Description of accounting policy for income tax</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Description of accounting policy for intangible assets [text block]</t>
+          <t>Description of accounting policy for intangible assets</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Description of accounting policy for interest income and expense [text block]</t>
+          <t>Description of accounting policy for interest income and expense</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Description of accounting policy for inventories [text block]</t>
+          <t>Description of accounting policy for inventories</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Description of accounting policy for investment in associates [text block]</t>
+          <t>Description of accounting policy for investment in associates</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Description of accounting policy for investments in subsidiaries [text block]</t>
+          <t>Description of accounting policy for investments in subsidiaries</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Description of accounting policy for investment property [text block]</t>
+          <t>Description of accounting policy for investment property</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Description of accounting policy for investments in joint ventures [text block]</t>
+          <t>Description of accounting policy for investments in joint ventures</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Description of accounting policy for issue expenses [text block]</t>
+          <t>Description of accounting policy for issue expenses</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Description of accounting policy for leases [text block]</t>
+          <t>Description of accounting policy for leases</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Description of accounting policy for non-current assets or disposal groups classified as held for sale and discontinued operations [text block]</t>
+          <t>Description of accounting policy for non-current assets or disposal groups classified as held for sale and discontinued operations</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Description of accounting policy for onerous contracts [text block]</t>
+          <t>Description of accounting policy for onerous contracts</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Description of accounting policy for preference share capital [text block]</t>
+          <t>Description of accounting policy for preference share capital</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Description of accounting policy for property, plant and equipment [text block]</t>
+          <t>Description of accounting policy for property, plant and equipment</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Description of accounting policy for provisions [text block]</t>
+          <t>Description of accounting policy for provisions</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Description of accounting policy for rental income [text block]</t>
+          <t>Description of accounting policy for rental income</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Description of accounting policy for restructuring [text block]</t>
+          <t>Description of accounting policy for restructuring</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Description of accounting policy for revenue and other income [text block]</t>
+          <t>Description of accounting policy for revenue and other income</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Description of accounting policy for segment reporting [text block]</t>
+          <t>Description of accounting policy for segment reporting</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Description of accounting policy for state plans [text block]</t>
+          <t>Description of accounting policy for state plans</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Description of accounting policy for transactions with related parties [text block]</t>
+          <t>Description of accounting policy for transactions with related parties</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Description of accounting policy for warranties [text block]</t>
+          <t>Description of accounting policy for warranties</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Description of other significant accounting policies relevant to understanding of financial statements [text block]</t>
+          <t>Description of other significant accounting policies relevant to understanding of financial statements</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Description of accounting policy for basis of consolidation [text block]</t>
+          <t>Description of accounting policy for basis of consolidation</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Description of accounting policy for basis of preparation of financial statements [text block]</t>
+          <t>Description of accounting policy for basis of preparation of financial statements</t>
         </is>
       </c>
     </row>

--- a/XBRL-template-MPERS/Company/12-Notes-AccountingPolicies.xlsx
+++ b/XBRL-template-MPERS/Company/12-Notes-AccountingPolicies.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,23 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+        <bgColor rgb="FF1F3864"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +56,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -440,7 +451,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Disclosure on summary significant accounting policies</t>
         </is>
